--- a/گزارش مدرسان - نمونه گزارش پرشده.xlsx
+++ b/گزارش مدرسان - نمونه گزارش پرشده.xlsx
@@ -11,8 +11,8 @@
     <sheet name="جزئیات کلاس‌ها" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'خلاصه مدرسان'!$A$2:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'جزئیات کلاس‌ها'!$A$2:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'خلاصه مدرسان'!$A$2:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'جزئیات کلاس‌ها'!$A$2:$K$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -136,14 +136,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>460</v>
@@ -580,7 +580,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>سوادرسانه حضوری: 3، سوادرسانه مجازی (لایو): 1، توانمندسازی گردان: 1</t>
+          <t>سوادرسانه حضوری: 3، سوادرسانه مجازی (لایو): 1، توانمندسازی گردان: 1، تولیدات : 1</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>255</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>سوادرسانه حضوری: 1، سوادرسانه مجازی (لایو): 1، توانمندسازی گردان: 1</t>
+          <t>سوادرسانه حضوری: 1، سوادرسانه مجازی (لایو): 1، توانمندسازی گردان: 1، تولیدات : 1</t>
         </is>
       </c>
     </row>
@@ -638,40 +638,68 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
+          <t>سعید نوری</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>تولیدات : 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
           <t>حسین موسوی</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D7" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E7" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>سوادرسانه مجازی (لایو): 1</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="9" t="n"/>
-      <c r="B7" s="9" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>جمع کل</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
+      <c r="C8" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F6"/>
+  <autoFilter ref="A2:F7"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -685,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -766,47 +794,47 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="n">
+      <c r="A3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>محمد رضایی</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>سوادرسانه حضوری</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>1405/06/02</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>ناحیه ۱</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>سواد رسانه‌ای پایه</t>
         </is>
       </c>
-      <c r="G3" s="10" t="n">
+      <c r="G3" s="9" t="n">
         <v>90</v>
       </c>
-      <c r="H3" s="10" t="n">
+      <c r="H3" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>سالن شهید بهشتی</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr"/>
-      <c r="K3" s="11" t="inlineStr"/>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -852,47 +880,47 @@
       <c r="K4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>محمد رضایی</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>سوادرسانه حضوری</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>1405/06/15</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>ناحیه ۲</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>سواد رسانه‌ای پایه</t>
         </is>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="9" t="n">
         <v>90</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>مدرسه</t>
         </is>
       </c>
-      <c r="J5" s="10" t="inlineStr"/>
-      <c r="K5" s="11" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -942,51 +970,51 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>محمد رضایی</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>توانمندسازی گردان</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>1405/06/18</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>گردان الف</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>کارگاه عکاسی</t>
         </is>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H7" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>پایگاه</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>حضوری</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr"/>
+      <c r="K7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -994,89 +1022,81 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
+          <t>محمد رضایی</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تولیدات </t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>1405/06/22</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>ناحیه ۳</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>موشن‌گرافی جنگ شناختی</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>موشن</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
           <t>زهرا احمدی</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>سوادرسانه حضوری</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>1405/06/12</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>ناحیه ۳</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>جنگ شناختی</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G9" s="9" t="n">
         <v>75</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H9" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>سالن اجتماعات</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>زهرا احمدی</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>سوادرسانه مجازی (لایو)</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>1405/06/08</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>ناحیه ۲</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>لایو جنگ روایت‌ها</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>95</v>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>روبیکا</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr"/>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>https://link2</t>
-        </is>
-      </c>
+      <c r="J9" s="9" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1089,84 +1109,88 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
+          <t>سوادرسانه مجازی (لایو)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>1405/06/08</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>ناحیه ۲</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>لایو جنگ روایت‌ها</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>روبیکا</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>https://link2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>زهرا احمدی</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
           <t>توانمندسازی گردان</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>1405/06/04</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>گردان الف</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>کارگاه تولید محتوا</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G11" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H11" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>پایگاه</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>حضوری</t>
         </is>
       </c>
-      <c r="K10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>علی کریمی</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>سوادرسانه حضوری</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>1405/06/05</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>ناحیه ۲</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>اخبار جعلی</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>مسجد جامع</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr"/>
-      <c r="K11" s="11" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1174,93 +1198,85 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
+          <t>زهرا احمدی</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تولیدات </t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>1405/06/06</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>ناحیه ۱</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>پوستر هفته دفاع مقدس</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>پوستر</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>https://p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
           <t>علی کریمی</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>سوادرسانه مجازی (لایو)</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>1405/06/03</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>ناحیه ۱</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>لایو سواد رسانه</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>110</v>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>اینستاگرام</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>https://link1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>علی کریمی</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>توانمندسازی گردان</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>1405/06/10</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>گردان ب</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>تحلیل رسانه</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>پایگاه</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>حضوری</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>سوادرسانه حضوری</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>1405/06/05</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>ناحیه ۲</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>اخبار جعلی</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>مسجد جامع</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -1268,45 +1284,221 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
+          <t>علی کریمی</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>سوادرسانه مجازی (لایو)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>1405/06/03</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>ناحیه ۱</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>لایو سواد رسانه</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>اینستاگرام</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr"/>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>https://link1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>علی کریمی</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>توانمندسازی گردان</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>1405/06/10</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>گردان ب</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>تحلیل رسانه</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>پایگاه</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>حضوری</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>سعید نوری</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تولیدات </t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>1405/06/11</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>ناحیه ۲</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>کلیپ سواد رسانه</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>کلیپ</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>https://p2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>سعید نوری</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تولیدات </t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>1405/06/14</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>ناحیه ۱</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>اینفوگرافی اخبار جعلی</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr"/>
+      <c r="H17" s="9" t="inlineStr"/>
+      <c r="I17" s="10" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>اینفوگرافی</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
           <t>حسین موسوی</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>سوادرسانه مجازی (لایو)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>1405/06/20</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>ناحیه ۳</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>لایو رسانه و نوجوان</t>
         </is>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G18" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H18" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>ایتا</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr"/>
-      <c r="K14" s="8" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr"/>
+      <c r="K18" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K14"/>
+  <autoFilter ref="A2:K18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
